--- a/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N47_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T2S0007_W0047F0002T0006Z000C1N47_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.62700106352216</v>
+        <v>5.626887672822351</v>
       </c>
       <c r="D2" t="n">
-        <v>30.46478240212922</v>
+        <v>4.950527140345998</v>
       </c>
       <c r="E2" t="n">
-        <v>15.48444069754892</v>
+        <v>2.516221613351699</v>
       </c>
       <c r="F2" t="n">
-        <v>14.87051380443006</v>
+        <v>2.416458493219884</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>16.30526608653979</v>
+        <v>2.649605739062716</v>
       </c>
       <c r="D3" t="n">
-        <v>14.09599892022847</v>
+        <v>2.290599824537126</v>
       </c>
       <c r="E3" t="n">
-        <v>15.48444069754892</v>
+        <v>2.516221613351699</v>
       </c>
       <c r="F3" t="n">
-        <v>14.87051380443006</v>
+        <v>2.416458493219884</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>48.41794720680395</v>
+        <v>7.867916421105642</v>
       </c>
       <c r="D4" t="n">
-        <v>42.13148079864394</v>
+        <v>6.84636562977964</v>
       </c>
       <c r="E4" t="n">
-        <v>15.48444069754892</v>
+        <v>2.516221613351699</v>
       </c>
       <c r="F4" t="n">
-        <v>14.87051380443006</v>
+        <v>2.416458493219884</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>32.63285567070994</v>
+        <v>5.302839046490365</v>
       </c>
       <c r="D5" t="n">
-        <v>25.59093880079519</v>
+        <v>4.158527555129219</v>
       </c>
       <c r="E5" t="n">
-        <v>15.48444069754892</v>
+        <v>2.516221613351699</v>
       </c>
       <c r="F5" t="n">
-        <v>14.87051380443006</v>
+        <v>2.416458493219884</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.54386099471128</v>
+        <v>5.125877411640583</v>
       </c>
       <c r="D6" t="n">
-        <v>24.0628067758955</v>
+        <v>3.910206101083018</v>
       </c>
       <c r="E6" t="n">
-        <v>15.48444069754892</v>
+        <v>2.516221613351699</v>
       </c>
       <c r="F6" t="n">
-        <v>14.87051380443006</v>
+        <v>2.416458493219884</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>64.30556760155307</v>
+        <v>10.44965473525237</v>
       </c>
       <c r="D7" t="n">
-        <v>56.86549660835277</v>
+        <v>9.240643198857326</v>
       </c>
       <c r="E7" t="n">
-        <v>15.48444069754892</v>
+        <v>2.516221613351699</v>
       </c>
       <c r="F7" t="n">
-        <v>14.87051380443006</v>
+        <v>2.416458493219884</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>52.15935880572972</v>
+        <v>8.47589580593108</v>
       </c>
       <c r="D8" t="n">
-        <v>47.19097170602743</v>
+        <v>7.668532902229458</v>
       </c>
       <c r="E8" t="n">
-        <v>15.48444069754892</v>
+        <v>2.516221613351699</v>
       </c>
       <c r="F8" t="n">
-        <v>14.87051380443006</v>
+        <v>2.416458493219884</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>61.18050393722844</v>
+        <v>9.941831889799623</v>
       </c>
       <c r="D9" t="n">
-        <v>56.48047642158378</v>
+        <v>9.178077418507364</v>
       </c>
       <c r="E9" t="n">
-        <v>15.48444069754892</v>
+        <v>2.516221613351699</v>
       </c>
       <c r="F9" t="n">
-        <v>14.87051380443006</v>
+        <v>2.416458493219884</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
